--- a/data/trans_bre/IP16A10-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 0,0</t>
+          <t>-14,39; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 0,0</t>
+          <t>-12,65; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,27 +714,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 9,36</t>
+          <t>0,66; 9,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 1,35</t>
+          <t>-5,0; 1,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,69</t>
+          <t>-3,19; 1,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,61; —</t>
+          <t>-20,63; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 147,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 16,12</t>
+          <t>-1,26; 17,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,49</t>
+          <t>0,0; 11,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 3,3</t>
+          <t>-6,96; 3,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,27 +874,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 7,3</t>
+          <t>0,28; 7,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,0</t>
+          <t>-2,66; 2,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,44</t>
+          <t>-2,55; 1,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 906,92</t>
+          <t>-13,86; 1116,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,03; 267,22</t>
+          <t>-80,37; 296,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 0,0</t>
+          <t>-16,2; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 0,0</t>
+          <t>-14,86; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,27 +714,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 9,46</t>
+          <t>0,38; 9,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,01</t>
+          <t>-4,71; 1,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,74</t>
+          <t>-3,24; 1,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,63; —</t>
+          <t>-32,12; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 147,87</t>
+          <t>-100,0; 223,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 17,48</t>
+          <t>-1,62; 17,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,51</t>
+          <t>0,0; 11,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 3,14</t>
+          <t>-5,35; 4,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,27 +874,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 7,5</t>
+          <t>-0,18; 7,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,2</t>
+          <t>-2,81; 1,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,45</t>
+          <t>-2,34; 1,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 1116,56</t>
+          <t>-35,9; 877,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,37; 296,93</t>
+          <t>-81,02; 224,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Estudios-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumieron  medicamentos para la diarrea</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 0,0</t>
+          <t>-13,93; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 0,0</t>
+          <t>-13,27; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,27 +714,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 9,49</t>
+          <t>0,44; 9,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 1,42</t>
+          <t>-4,94; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,69</t>
+          <t>-3,09; 1,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,12; —</t>
+          <t>-39,61; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 223,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 17,57</t>
+          <t>-1,66; 16,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,19</t>
+          <t>0,0; 11,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 4,47</t>
+          <t>-5,53; 3,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,27 +874,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 7,09</t>
+          <t>0,24; 7,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,84</t>
+          <t>-2,73; 2,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,56</t>
+          <t>-2,4; 1,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 877,06</t>
+          <t>-14,46; 906,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,02; 224,58</t>
+          <t>-80,03; 267,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,139 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,66</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.7393654624920608</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.7092397263353969</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-13,93; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-13,27; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.196302798757661</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.61159195198908</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,78</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,37</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>300,78%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-48,05%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-22,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,44; 9,36</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,94; 1,35</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,09; 1,69</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-39,61; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.9424737367200212</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.3291729552285154</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.03801838447402683</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>3.229565667309551</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4657326425091493</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1327798207148409</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,42</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,46</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>278,93%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-11,39%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1276749064885103</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.229040878287432</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.6347065506110613</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.3906905446858104</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,66; 16,12</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,49</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,53; 3,3</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.965926278308178</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.3485223296067161</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.3858917049779421</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>1.941748816700065</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +743,147 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>185,6%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-17,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-22,14%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.5206817783638971</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9524590868382591</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.01241050734842055</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1.201329849748935</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.03510493554974753</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,24; 7,3</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,73; 2,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 1,44</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-14,46; 906,92</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-80,03; 267,22</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.8673462375330102</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.062172914381651</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.870402015531454</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.296692920676783</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9925802414755469</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.6213185863892896</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.08251226164849579</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.02673525807112931</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1.649484329867334</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1510655040248301</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.09656382904025769</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.01270271001505337</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.6443129410973134</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.4986557574116259</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.1845672126252996</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.78557644433198</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.330049804944717</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5352153784106032</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.3360738048872841</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>10.17037195161851</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.746727941659791</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +892,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
